--- a/artfynd/A 41246-2024 artfynd.xlsx
+++ b/artfynd/A 41246-2024 artfynd.xlsx
@@ -4776,7 +4776,7 @@
         <v>120848392</v>
       </c>
       <c r="B42" t="n">
-        <v>56552</v>
+        <v>56555</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>120742266</v>
       </c>
       <c r="B43" t="n">
-        <v>91031</v>
+        <v>91041</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41246-2024 artfynd.xlsx
+++ b/artfynd/A 41246-2024 artfynd.xlsx
@@ -4878,7 +4878,7 @@
         <v>120742266</v>
       </c>
       <c r="B43" t="n">
-        <v>91041</v>
+        <v>91053</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41246-2024 artfynd.xlsx
+++ b/artfynd/A 41246-2024 artfynd.xlsx
@@ -4878,7 +4878,7 @@
         <v>120742266</v>
       </c>
       <c r="B43" t="n">
-        <v>91053</v>
+        <v>91054</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41246-2024 artfynd.xlsx
+++ b/artfynd/A 41246-2024 artfynd.xlsx
@@ -4878,7 +4878,7 @@
         <v>120742266</v>
       </c>
       <c r="B43" t="n">
-        <v>91054</v>
+        <v>91057</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41246-2024 artfynd.xlsx
+++ b/artfynd/A 41246-2024 artfynd.xlsx
@@ -4878,7 +4878,7 @@
         <v>120742266</v>
       </c>
       <c r="B43" t="n">
-        <v>91057</v>
+        <v>91063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/artfynd/A 41246-2024 artfynd.xlsx
+++ b/artfynd/A 41246-2024 artfynd.xlsx
@@ -4878,7 +4878,7 @@
         <v>120742266</v>
       </c>
       <c r="B43" t="n">
-        <v>91063</v>
+        <v>91064</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
